--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 11:21</t>
+    <t xml:space="preserve">2026-08-19 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:12</t>
+    <t xml:space="preserve">2026-08-28 15:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:09</t>
+    <t xml:space="preserve">2026-08-29 05:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,13 +474,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.32</v>
+        <v>14.64</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>10.4</v>
+        <v>20.8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.08</v>
+        <v>6.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2024_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:45</t>
+    <t xml:space="preserve">2026-09-07 11:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
